--- a/mosip_master/xlsx/screen_authorization.xlsx
+++ b/mosip_master/xlsx/screen_authorization.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tf_nira\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NIRA-DEV\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC87BE28-3992-429D-A7E4-9F62CAAF52D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{747699DA-CD9B-4EAA-9720-33D230FA83D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$1</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="20">
   <si>
     <t>lang_code</t>
   </si>
@@ -82,6 +85,9 @@
   </si>
   <si>
     <t>getFirstIdRoot</t>
+  </si>
+  <si>
+    <t>renewUINRoot</t>
   </si>
 </sst>
 </file>
@@ -138,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -147,6 +153,7 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -455,11 +462,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
-    <col min="2" max="2" width="19.85546875" customWidth="1"/>
+    <col min="2" max="2" width="44.42578125" customWidth="1"/>
     <col min="3" max="3" width="26.7109375" customWidth="1"/>
     <col min="4" max="4" width="15.42578125" style="1" customWidth="1"/>
     <col min="5" max="5" width="9.140625" style="1" customWidth="1"/>
@@ -487,10 +494,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>8</v>
@@ -504,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>8</v>
@@ -521,10 +528,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>8</v>
@@ -538,10 +545,10 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>8</v>
@@ -555,10 +562,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>8</v>
@@ -572,10 +579,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>8</v>
@@ -589,7 +596,7 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
@@ -606,10 +613,10 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>8</v>
@@ -623,10 +630,10 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>8</v>
@@ -640,10 +647,10 @@
         <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>8</v>
@@ -657,10 +664,10 @@
         <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>8</v>
@@ -674,10 +681,10 @@
         <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>8</v>
@@ -691,10 +698,10 @@
         <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>8</v>
@@ -708,10 +715,10 @@
         <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>8</v>
@@ -725,10 +732,10 @@
         <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>8</v>
@@ -742,10 +749,10 @@
         <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>8</v>
@@ -759,7 +766,7 @@
         <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C18" t="s">
         <v>7</v>
@@ -776,7 +783,7 @@
         <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C19" t="s">
         <v>9</v>
@@ -793,7 +800,7 @@
         <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C20" t="s">
         <v>12</v>
@@ -810,7 +817,7 @@
         <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="s">
         <v>7</v>
@@ -827,7 +834,7 @@
         <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C22" t="s">
         <v>9</v>
@@ -844,7 +851,7 @@
         <v>5</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
@@ -861,10 +868,10 @@
         <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C24" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>8</v>
@@ -878,17 +885,77 @@
         <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C25" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" t="s">
         <v>7</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>8</v>
-      </c>
+      <c r="D26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H36" s="4"/>
+    </row>
+    <row r="37" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H37" s="4"/>
+    </row>
+    <row r="38" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H38" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
